--- a/dados/excel/histograma_salarial.xlsx
+++ b/dados/excel/histograma_salarial.xlsx
@@ -7,18 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Metadados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +32,37 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000D2B4E"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="004A5568"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="004A5568"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +71,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00003A70"/>
-        <bgColor rgb="00003A70"/>
+        <fgColor rgb="000D2B4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -58,25 +89,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color rgb="004A90D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D8DEE6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D8DEE6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8DEE6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8DEE6"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,287 +509,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FAIXA</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SERVIDORES</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>FOLHA (R$)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MÊS</t>
+          <t>Histograma salarial</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ate_2k</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2552812.29</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2k_4k</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>1418</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>4496073.96</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>Fonte: Portal da Transparência de Sorocaba · Organizado pelo Observatório Social do Brasil — Sorocaba · Licença CC-BY 4.0</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>4k_6k</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2814</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>13992918.37</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6k_8k</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1739</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12054458.84</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Para que serve</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Quantos ganham cada valor.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>8k_10k</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9232299.51</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Informações técnicas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>10k_15k</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2431</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>30248368.1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>histograma_salarial.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>15k_20k</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>1188</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>20212071.73</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Servidores por faixa de remuneração.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20k_30k</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>14954263.63</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Linhas</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>acima_30k</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9688944.08</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Colunas</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Separador</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ponto e vírgula</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Codificação</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>utf-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Gerado em</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>24/09/2026 19:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Dicionário de colunas</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Coluna</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Formato no Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>﻿faixa</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Número decimal (#,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Número inteiro (#,##0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>folha</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>moeda</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Moeda (R$ #,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Número inteiro (#,##0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Número inteiro (#,##0)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -734,86 +755,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CAMPO</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>VALOR</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>﻿faixa</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>folha</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>mes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>FONTE</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Portal da Transparência de Sorocaba</t>
-        </is>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>ate_2k</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>2349</v>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>2552812.29</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>https://transparencia.sorocaba.sp.gov.br</t>
-        </is>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>2k_4k</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>1418</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>4496073.96</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>PERÍODO</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>2022-01 a 2026-08</t>
-        </is>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>4k_6k</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>2814</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>13992918.37</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>LICENÇA</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 — Observatório Social do Brasil — Sorocaba</t>
-        </is>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>6k_8k</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>1739</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>12054458.84</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>GERADO EM</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23 18:50</t>
-        </is>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>8k_10k</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>1034</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>9232299.51</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>10k_15k</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>2431</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>30248368.1</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>15k_20k</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>1188</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>20212071.73</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>20k_30k</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>626</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>14954263.63</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>acima_30k</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>230</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>9688944.08</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados/excel/histograma_salarial.xlsx
+++ b/dados/excel/histograma_salarial.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -799,16 +799,16 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>2349</v>
+        <v>1508</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2552812.29</v>
+        <v>1514525.13</v>
       </c>
       <c r="D2" s="9" t="n">
         <v>2026</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>1418</v>
+        <v>2735</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>4496073.96</v>
+        <v>8269406</v>
       </c>
       <c r="D3" s="12" t="n">
         <v>2026</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -837,16 +837,16 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>2814</v>
+        <v>2801</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>13992918.37</v>
+        <v>13980214.18</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>2026</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>1739</v>
+        <v>1750</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>12054458.84</v>
+        <v>12143771.87</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>2026</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -875,16 +875,16 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>1034</v>
+        <v>1066</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>9232299.51</v>
+        <v>9505088.609999999</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>2026</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>2431</v>
+        <v>2444</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>30248368.1</v>
+        <v>30467020.19</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>2026</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>20212071.73</v>
+        <v>20092961.35</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>2026</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>14954263.63</v>
+        <v>15303770.49</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>2026</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>9688944.08</v>
+        <v>10004042.95</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>2026</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
